--- a/mau-bang-cham-cong.xlsx
+++ b/mau-bang-cham-cong.xlsx
@@ -5,14 +5,13 @@
   <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <sheets>
     <sheet sheetId="1" name="Tháng 9-2026" state="visible" r:id="rId4"/>
-    <sheet sheetId="2" name="Chi tiết &amp; ảnh" state="visible" r:id="rId5"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="41">
   <si>
     <t>BẢNG CHẤM CÔNG THÁNG 9/2026</t>
   </si>
@@ -20,7 +19,7 @@
     <t>Nhân viên: Quanglam  ·  Email: quanglam@gmail.com</t>
   </si>
   <si>
-    <t>Giờ quy định 08:30 – 17:00  ·  Mất chuyên cần khi muộn + sớm ≥ 60 phút/tháng  ·  Xuất ngày 30/09/2026  ·  Ảnh chấm công xem ở sheet “Chi tiết &amp; ảnh”</t>
+    <t>Giờ quy định 08:30 – 17:00  ·  Mất chuyên cần khi muộn + sớm ≥ 60 phút/tháng  ·  Xuất ngày 30/09/2026</t>
   </si>
   <si>
     <t>Ngày</t>
@@ -50,6 +49,12 @@
     <t>Ghi chú</t>
   </si>
   <si>
+    <t>Ảnh vào</t>
+  </si>
+  <si>
+    <t>Ảnh ra</t>
+  </si>
+  <si>
     <t>T3</t>
   </si>
   <si>
@@ -59,13 +64,16 @@
     <t/>
   </si>
   <si>
+    <t>Không có ảnh</t>
+  </si>
+  <si>
     <t>T4</t>
   </si>
   <si>
     <t>Muộn/sớm</t>
   </si>
   <si>
-    <t>kẹt xe</t>
+    <t>kẹt xe; Giờ vào đã sửa (gốc 08:52)</t>
   </si>
   <si>
     <t>T5</t>
@@ -104,6 +112,9 @@
     <t>Trong đó làm online</t>
   </si>
   <si>
+    <t>Trong đó nghỉ có công</t>
+  </si>
+  <si>
     <t>Tổng đi muộn + về sớm (phút)</t>
   </si>
   <si>
@@ -123,39 +134,6 @@
   </si>
   <si>
     <t>Tạm tính đến 30/09/2026</t>
-  </si>
-  <si>
-    <t>CHI TIẾT LẦN CHẤM CÔNG THÁNG 9/2026</t>
-  </si>
-  <si>
-    <t>Mỗi dòng là một lần chấm kèm ảnh chụp máy chấm công  ·  Xuất ngày 30/09/2026</t>
-  </si>
-  <si>
-    <t>Loại</t>
-  </si>
-  <si>
-    <t>Giờ</t>
-  </si>
-  <si>
-    <t>Nguồn giờ</t>
-  </si>
-  <si>
-    <t>Ảnh chấm công</t>
-  </si>
-  <si>
-    <t>Vào</t>
-  </si>
-  <si>
-    <t>Theo giờ chụp ảnh</t>
-  </si>
-  <si>
-    <t>Ra</t>
-  </si>
-  <si>
-    <t>Không có ảnh</t>
-  </si>
-  <si>
-    <t>Giờ tải lên (đã sửa, gốc 08:52)</t>
   </si>
 </sst>
 </file>
@@ -166,7 +144,7 @@
     <numFmt numFmtId="164" formatCode="dd/mm/yyyy"/>
     <numFmt numFmtId="165" formatCode="hh:mm"/>
   </numFmts>
-  <fonts count="15" x14ac:knownFonts="1">
+  <fonts count="14" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -224,10 +202,6 @@
       <b/>
       <color rgb="FF1D4ED8"/>
       <sz val="13"/>
-    </font>
-    <font>
-      <b/>
-      <color rgb="FF1D4ED8"/>
     </font>
   </fonts>
   <fills count="12">
@@ -315,7 +289,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -347,6 +321,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="165" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -371,6 +348,9 @@
     <xf numFmtId="165" fontId="11" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="11" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -384,15 +364,6 @@
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -416,12 +387,12 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:oneCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>11818</xdr:colOff>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>10377</xdr:colOff>
       <xdr:row>4</xdr:row>
-      <xdr:rowOff>37499</xdr:rowOff>
+      <xdr:rowOff>37500</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="1619250" cy="1219200"/>
+    <xdr:ext cx="1371600" cy="1028700"/>
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="1" name="Picture 1">
@@ -455,12 +426,12 @@
   </xdr:oneCellAnchor>
   <xdr:oneCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>11818</xdr:colOff>
-      <xdr:row>6</xdr:row>
-      <xdr:rowOff>37499</xdr:rowOff>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>10377</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>37500</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="1619250" cy="1219200"/>
+    <xdr:ext cx="1371600" cy="1028700"/>
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="2" name="Picture 2">
@@ -820,7 +791,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I45"/>
+  <dimension ref="A1:K46"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="13" customWidth="1"/>
@@ -829,10 +800,11 @@
     <col min="5" max="6" width="12" customWidth="1"/>
     <col min="7" max="7" width="8" customWidth="1"/>
     <col min="8" max="8" width="15" customWidth="1"/>
-    <col min="9" max="9" width="36" customWidth="1"/>
+    <col min="9" max="9" width="30" customWidth="1"/>
+    <col min="10" max="11" width="22" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" ht="32" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -844,8 +816,10 @@
       <c r="G1" s="1"/>
       <c r="H1" s="1"/>
       <c r="I1" s="1"/>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J1" s="1"/>
+      <c r="K1" s="1"/>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
@@ -857,8 +831,10 @@
       <c r="G2" s="2"/>
       <c r="H2" s="2"/>
       <c r="I2" s="2"/>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J2" s="2"/>
+      <c r="K2" s="2"/>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>2</v>
       </c>
@@ -870,8 +846,10 @@
       <c r="G3" s="3"/>
       <c r="H3" s="3"/>
       <c r="I3" s="3"/>
-    </row>
-    <row r="4" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J3" s="3"/>
+      <c r="K3" s="3"/>
+    </row>
+    <row r="4" ht="24" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
         <v>3</v>
       </c>
@@ -899,13 +877,19 @@
       <c r="I4" s="4" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J4" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="K4" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="5" ht="88.5" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" s="5">
         <v>46266</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C5" s="7">
         <v>0.3506944444444444</v>
@@ -919,85 +903,109 @@
         <v>1</v>
       </c>
       <c r="H5" s="9" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="I5" s="10" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+        <v>16</v>
+      </c>
+      <c r="J5" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="K5" s="11" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="6" ht="88.5" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" s="5">
         <v>46267</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="C6" s="11">
+        <v>18</v>
+      </c>
+      <c r="C6" s="12">
         <v>0.3680555555555556</v>
       </c>
-      <c r="D6" s="11">
+      <c r="D6" s="12">
         <v>0.6875</v>
       </c>
-      <c r="E6" s="12">
+      <c r="E6" s="13">
         <v>20</v>
       </c>
-      <c r="F6" s="12">
+      <c r="F6" s="13">
         <v>30</v>
       </c>
       <c r="G6" s="8">
         <v>1</v>
       </c>
-      <c r="H6" s="13" t="s">
-        <v>16</v>
+      <c r="H6" s="14" t="s">
+        <v>19</v>
       </c>
       <c r="I6" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="J6" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="K6" s="11" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" s="5">
         <v>46268</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="C7" s="7"/>
       <c r="D7" s="7"/>
       <c r="E7" s="6"/>
       <c r="F7" s="6"/>
       <c r="G7" s="6"/>
-      <c r="H7" s="14" t="s">
-        <v>19</v>
+      <c r="H7" s="15" t="s">
+        <v>22</v>
       </c>
       <c r="I7" s="10" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+        <v>16</v>
+      </c>
+      <c r="J7" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="K7" s="6" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" s="5">
         <v>46269</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="C8" s="7"/>
       <c r="D8" s="7"/>
       <c r="E8" s="6"/>
       <c r="F8" s="6"/>
       <c r="G8" s="6"/>
-      <c r="H8" s="14" t="s">
-        <v>19</v>
+      <c r="H8" s="15" t="s">
+        <v>22</v>
       </c>
       <c r="I8" s="10" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+        <v>16</v>
+      </c>
+      <c r="J8" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="K8" s="6" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" s="5">
         <v>46270</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="C9" s="7"/>
       <c r="D9" s="7"/>
@@ -1006,133 +1014,177 @@
       <c r="G9" s="8">
         <v>1</v>
       </c>
-      <c r="H9" s="15" t="s">
-        <v>22</v>
+      <c r="H9" s="16" t="s">
+        <v>25</v>
       </c>
       <c r="I9" s="10" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A10" s="16">
+        <v>16</v>
+      </c>
+      <c r="J9" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="K9" s="6" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A10" s="17">
         <v>46271</v>
       </c>
-      <c r="B10" s="17" t="s">
-        <v>23</v>
-      </c>
-      <c r="C10" s="18"/>
-      <c r="D10" s="18"/>
-      <c r="E10" s="17"/>
-      <c r="F10" s="17"/>
-      <c r="G10" s="17"/>
-      <c r="H10" s="17" t="s">
-        <v>24</v>
-      </c>
-      <c r="I10" s="19" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B10" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="C10" s="19"/>
+      <c r="D10" s="19"/>
+      <c r="E10" s="18"/>
+      <c r="F10" s="18"/>
+      <c r="G10" s="20">
+        <v>1</v>
+      </c>
+      <c r="H10" s="18" t="s">
+        <v>27</v>
+      </c>
+      <c r="I10" s="21" t="s">
+        <v>16</v>
+      </c>
+      <c r="J10" s="18" t="s">
+        <v>16</v>
+      </c>
+      <c r="K10" s="18" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" s="5">
         <v>46272</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="C11" s="7"/>
       <c r="D11" s="7"/>
       <c r="E11" s="6"/>
       <c r="F11" s="6"/>
       <c r="G11" s="6"/>
-      <c r="H11" s="14" t="s">
-        <v>19</v>
+      <c r="H11" s="15" t="s">
+        <v>22</v>
       </c>
       <c r="I11" s="10" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+        <v>16</v>
+      </c>
+      <c r="J11" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="K11" s="6" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" s="5">
         <v>46273</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C12" s="7"/>
       <c r="D12" s="7"/>
       <c r="E12" s="6"/>
       <c r="F12" s="6"/>
       <c r="G12" s="6"/>
-      <c r="H12" s="14" t="s">
-        <v>19</v>
+      <c r="H12" s="15" t="s">
+        <v>22</v>
       </c>
       <c r="I12" s="10" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+        <v>16</v>
+      </c>
+      <c r="J12" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="K12" s="6" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" s="5">
         <v>46274</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="C13" s="7"/>
       <c r="D13" s="7"/>
       <c r="E13" s="6"/>
       <c r="F13" s="6"/>
       <c r="G13" s="6"/>
-      <c r="H13" s="14" t="s">
-        <v>19</v>
+      <c r="H13" s="15" t="s">
+        <v>22</v>
       </c>
       <c r="I13" s="10" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+        <v>16</v>
+      </c>
+      <c r="J13" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="K13" s="6" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" s="5">
         <v>46275</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="C14" s="7"/>
       <c r="D14" s="7"/>
       <c r="E14" s="6"/>
       <c r="F14" s="6"/>
       <c r="G14" s="6"/>
-      <c r="H14" s="14" t="s">
-        <v>19</v>
+      <c r="H14" s="15" t="s">
+        <v>22</v>
       </c>
       <c r="I14" s="10" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+        <v>16</v>
+      </c>
+      <c r="J14" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="K14" s="6" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15" s="5">
         <v>46276</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="C15" s="7"/>
       <c r="D15" s="7"/>
       <c r="E15" s="6"/>
       <c r="F15" s="6"/>
       <c r="G15" s="6"/>
-      <c r="H15" s="14" t="s">
-        <v>19</v>
+      <c r="H15" s="15" t="s">
+        <v>22</v>
       </c>
       <c r="I15" s="10" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+        <v>16</v>
+      </c>
+      <c r="J15" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="K15" s="6" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16" s="5">
         <v>46277</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="C16" s="7"/>
       <c r="D16" s="7"/>
@@ -1141,133 +1193,177 @@
       <c r="G16" s="8">
         <v>1</v>
       </c>
-      <c r="H16" s="15" t="s">
-        <v>22</v>
+      <c r="H16" s="16" t="s">
+        <v>25</v>
       </c>
       <c r="I16" s="10" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A17" s="16">
+        <v>16</v>
+      </c>
+      <c r="J16" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="K16" s="6" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A17" s="17">
         <v>46278</v>
       </c>
-      <c r="B17" s="17" t="s">
-        <v>23</v>
-      </c>
-      <c r="C17" s="18"/>
-      <c r="D17" s="18"/>
-      <c r="E17" s="17"/>
-      <c r="F17" s="17"/>
-      <c r="G17" s="17"/>
-      <c r="H17" s="17" t="s">
-        <v>24</v>
-      </c>
-      <c r="I17" s="19" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B17" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="C17" s="19"/>
+      <c r="D17" s="19"/>
+      <c r="E17" s="18"/>
+      <c r="F17" s="18"/>
+      <c r="G17" s="20">
+        <v>1</v>
+      </c>
+      <c r="H17" s="18" t="s">
+        <v>27</v>
+      </c>
+      <c r="I17" s="21" t="s">
+        <v>16</v>
+      </c>
+      <c r="J17" s="18" t="s">
+        <v>16</v>
+      </c>
+      <c r="K17" s="18" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A18" s="5">
         <v>46279</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="C18" s="7"/>
       <c r="D18" s="7"/>
       <c r="E18" s="6"/>
       <c r="F18" s="6"/>
       <c r="G18" s="6"/>
-      <c r="H18" s="14" t="s">
-        <v>19</v>
+      <c r="H18" s="15" t="s">
+        <v>22</v>
       </c>
       <c r="I18" s="10" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
+        <v>16</v>
+      </c>
+      <c r="J18" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="K18" s="6" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A19" s="5">
         <v>46280</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C19" s="7"/>
       <c r="D19" s="7"/>
       <c r="E19" s="6"/>
       <c r="F19" s="6"/>
       <c r="G19" s="6"/>
-      <c r="H19" s="14" t="s">
-        <v>19</v>
+      <c r="H19" s="15" t="s">
+        <v>22</v>
       </c>
       <c r="I19" s="10" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
+        <v>16</v>
+      </c>
+      <c r="J19" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="K19" s="6" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A20" s="5">
         <v>46281</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="C20" s="7"/>
       <c r="D20" s="7"/>
       <c r="E20" s="6"/>
       <c r="F20" s="6"/>
       <c r="G20" s="6"/>
-      <c r="H20" s="14" t="s">
-        <v>19</v>
+      <c r="H20" s="15" t="s">
+        <v>22</v>
       </c>
       <c r="I20" s="10" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
+        <v>16</v>
+      </c>
+      <c r="J20" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="K20" s="6" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A21" s="5">
         <v>46282</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="C21" s="7"/>
       <c r="D21" s="7"/>
       <c r="E21" s="6"/>
       <c r="F21" s="6"/>
       <c r="G21" s="6"/>
-      <c r="H21" s="14" t="s">
-        <v>19</v>
+      <c r="H21" s="15" t="s">
+        <v>22</v>
       </c>
       <c r="I21" s="10" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
+        <v>16</v>
+      </c>
+      <c r="J21" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="K21" s="6" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A22" s="5">
         <v>46283</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="C22" s="7"/>
       <c r="D22" s="7"/>
       <c r="E22" s="6"/>
       <c r="F22" s="6"/>
       <c r="G22" s="6"/>
-      <c r="H22" s="14" t="s">
-        <v>19</v>
+      <c r="H22" s="15" t="s">
+        <v>22</v>
       </c>
       <c r="I22" s="10" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
+        <v>16</v>
+      </c>
+      <c r="J22" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="K22" s="6" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A23" s="5">
         <v>46284</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="C23" s="7"/>
       <c r="D23" s="7"/>
@@ -1276,133 +1372,177 @@
       <c r="G23" s="8">
         <v>1</v>
       </c>
-      <c r="H23" s="15" t="s">
-        <v>22</v>
+      <c r="H23" s="16" t="s">
+        <v>25</v>
       </c>
       <c r="I23" s="10" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A24" s="16">
+        <v>16</v>
+      </c>
+      <c r="J23" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="K23" s="6" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A24" s="17">
         <v>46285</v>
       </c>
-      <c r="B24" s="17" t="s">
-        <v>23</v>
-      </c>
-      <c r="C24" s="18"/>
-      <c r="D24" s="18"/>
-      <c r="E24" s="17"/>
-      <c r="F24" s="17"/>
-      <c r="G24" s="17"/>
-      <c r="H24" s="17" t="s">
-        <v>24</v>
-      </c>
-      <c r="I24" s="19" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B24" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="C24" s="19"/>
+      <c r="D24" s="19"/>
+      <c r="E24" s="18"/>
+      <c r="F24" s="18"/>
+      <c r="G24" s="20">
+        <v>1</v>
+      </c>
+      <c r="H24" s="18" t="s">
+        <v>27</v>
+      </c>
+      <c r="I24" s="21" t="s">
+        <v>16</v>
+      </c>
+      <c r="J24" s="18" t="s">
+        <v>16</v>
+      </c>
+      <c r="K24" s="18" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A25" s="5">
         <v>46286</v>
       </c>
       <c r="B25" s="6" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="C25" s="7"/>
       <c r="D25" s="7"/>
       <c r="E25" s="6"/>
       <c r="F25" s="6"/>
       <c r="G25" s="6"/>
-      <c r="H25" s="14" t="s">
-        <v>19</v>
+      <c r="H25" s="15" t="s">
+        <v>22</v>
       </c>
       <c r="I25" s="10" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
+        <v>16</v>
+      </c>
+      <c r="J25" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="K25" s="6" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A26" s="5">
         <v>46287</v>
       </c>
       <c r="B26" s="6" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C26" s="7"/>
       <c r="D26" s="7"/>
       <c r="E26" s="6"/>
       <c r="F26" s="6"/>
       <c r="G26" s="6"/>
-      <c r="H26" s="14" t="s">
-        <v>19</v>
+      <c r="H26" s="15" t="s">
+        <v>22</v>
       </c>
       <c r="I26" s="10" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
+        <v>16</v>
+      </c>
+      <c r="J26" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="K26" s="6" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A27" s="5">
         <v>46288</v>
       </c>
       <c r="B27" s="6" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="C27" s="7"/>
       <c r="D27" s="7"/>
       <c r="E27" s="6"/>
       <c r="F27" s="6"/>
       <c r="G27" s="6"/>
-      <c r="H27" s="14" t="s">
-        <v>19</v>
+      <c r="H27" s="15" t="s">
+        <v>22</v>
       </c>
       <c r="I27" s="10" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
+        <v>16</v>
+      </c>
+      <c r="J27" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="K27" s="6" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A28" s="5">
         <v>46289</v>
       </c>
       <c r="B28" s="6" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="C28" s="7"/>
       <c r="D28" s="7"/>
       <c r="E28" s="6"/>
       <c r="F28" s="6"/>
       <c r="G28" s="6"/>
-      <c r="H28" s="14" t="s">
-        <v>19</v>
+      <c r="H28" s="15" t="s">
+        <v>22</v>
       </c>
       <c r="I28" s="10" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
+        <v>16</v>
+      </c>
+      <c r="J28" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="K28" s="6" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A29" s="5">
         <v>46290</v>
       </c>
       <c r="B29" s="6" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="C29" s="7"/>
       <c r="D29" s="7"/>
       <c r="E29" s="6"/>
       <c r="F29" s="6"/>
       <c r="G29" s="6"/>
-      <c r="H29" s="14" t="s">
-        <v>19</v>
+      <c r="H29" s="15" t="s">
+        <v>22</v>
       </c>
       <c r="I29" s="10" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
+        <v>16</v>
+      </c>
+      <c r="J29" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="K29" s="6" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A30" s="5">
         <v>46291</v>
       </c>
       <c r="B30" s="6" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="C30" s="7"/>
       <c r="D30" s="7"/>
@@ -1411,145 +1551,179 @@
       <c r="G30" s="8">
         <v>1</v>
       </c>
-      <c r="H30" s="15" t="s">
-        <v>22</v>
+      <c r="H30" s="16" t="s">
+        <v>25</v>
       </c>
       <c r="I30" s="10" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A31" s="16">
+        <v>16</v>
+      </c>
+      <c r="J30" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="K30" s="6" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A31" s="17">
         <v>46292</v>
       </c>
-      <c r="B31" s="17" t="s">
-        <v>23</v>
-      </c>
-      <c r="C31" s="18"/>
-      <c r="D31" s="18"/>
-      <c r="E31" s="17"/>
-      <c r="F31" s="17"/>
-      <c r="G31" s="17"/>
-      <c r="H31" s="17" t="s">
-        <v>24</v>
-      </c>
-      <c r="I31" s="19" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B31" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="C31" s="19"/>
+      <c r="D31" s="19"/>
+      <c r="E31" s="18"/>
+      <c r="F31" s="18"/>
+      <c r="G31" s="20">
+        <v>1</v>
+      </c>
+      <c r="H31" s="18" t="s">
+        <v>27</v>
+      </c>
+      <c r="I31" s="21" t="s">
+        <v>16</v>
+      </c>
+      <c r="J31" s="18" t="s">
+        <v>16</v>
+      </c>
+      <c r="K31" s="18" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A32" s="5">
         <v>46293</v>
       </c>
       <c r="B32" s="6" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="C32" s="7"/>
       <c r="D32" s="7"/>
       <c r="E32" s="6"/>
       <c r="F32" s="6"/>
       <c r="G32" s="6"/>
-      <c r="H32" s="14" t="s">
-        <v>19</v>
+      <c r="H32" s="15" t="s">
+        <v>22</v>
       </c>
       <c r="I32" s="10" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
+        <v>16</v>
+      </c>
+      <c r="J32" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="K32" s="6" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="33" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A33" s="5">
         <v>46294</v>
       </c>
       <c r="B33" s="6" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C33" s="7"/>
       <c r="D33" s="7"/>
       <c r="E33" s="6"/>
       <c r="F33" s="6"/>
       <c r="G33" s="6"/>
-      <c r="H33" s="14" t="s">
-        <v>19</v>
+      <c r="H33" s="15" t="s">
+        <v>22</v>
       </c>
       <c r="I33" s="10" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
+        <v>16</v>
+      </c>
+      <c r="J33" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="K33" s="6" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="34" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A34" s="5">
         <v>46295</v>
       </c>
       <c r="B34" s="6" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="C34" s="7"/>
       <c r="D34" s="7"/>
       <c r="E34" s="6"/>
       <c r="F34" s="6"/>
       <c r="G34" s="6"/>
-      <c r="H34" s="20" t="s">
-        <v>14</v>
+      <c r="H34" s="22" t="s">
+        <v>16</v>
       </c>
       <c r="I34" s="10" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="35" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A35" s="21" t="s">
-        <v>26</v>
-      </c>
-      <c r="B35" s="21"/>
-      <c r="C35" s="21"/>
-      <c r="D35" s="21"/>
-      <c r="E35" s="21">
+        <v>16</v>
+      </c>
+      <c r="J34" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="K34" s="6" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="35" ht="22" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A35" s="23" t="s">
+        <v>29</v>
+      </c>
+      <c r="B35" s="23"/>
+      <c r="C35" s="23"/>
+      <c r="D35" s="23"/>
+      <c r="E35" s="23">
         <f>SUM(E5:E34)</f>
         <v>20</v>
       </c>
-      <c r="F35" s="21">
+      <c r="F35" s="23">
         <f>SUM(F5:F34)</f>
         <v>30</v>
       </c>
-      <c r="G35" s="21">
+      <c r="G35" s="23">
         <f>SUM(G5:G34)</f>
-        <v>6</v>
-      </c>
-      <c r="H35" s="21"/>
-      <c r="I35" s="21"/>
+        <v>10</v>
+      </c>
+      <c r="H35" s="23"/>
+      <c r="I35" s="23"/>
+      <c r="J35" s="23"/>
+      <c r="K35" s="23"/>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A37" s="22" t="s">
-        <v>27</v>
-      </c>
-      <c r="B37" s="22"/>
-      <c r="C37" s="22"/>
-      <c r="D37" s="22"/>
-      <c r="E37" s="23">
+      <c r="A37" s="24" t="s">
+        <v>30</v>
+      </c>
+      <c r="B37" s="24"/>
+      <c r="C37" s="24"/>
+      <c r="D37" s="24"/>
+      <c r="E37" s="25">
         <f>G35</f>
-        <v>6</v>
-      </c>
-      <c r="F37" s="23"/>
-      <c r="G37" s="23"/>
+        <v>10</v>
+      </c>
+      <c r="F37" s="25"/>
+      <c r="G37" s="25"/>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A38" s="22" t="s">
-        <v>28</v>
-      </c>
-      <c r="B38" s="22"/>
-      <c r="C38" s="22"/>
-      <c r="D38" s="22"/>
+      <c r="A38" s="24" t="s">
+        <v>31</v>
+      </c>
+      <c r="B38" s="24"/>
+      <c r="C38" s="24"/>
+      <c r="D38" s="24"/>
       <c r="E38" s="8">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="F38" s="8"/>
       <c r="G38" s="8"/>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A39" s="22" t="s">
-        <v>29</v>
-      </c>
-      <c r="B39" s="22"/>
-      <c r="C39" s="22"/>
-      <c r="D39" s="22"/>
+      <c r="A39" s="24" t="s">
+        <v>32</v>
+      </c>
+      <c r="B39" s="24"/>
+      <c r="C39" s="24"/>
+      <c r="D39" s="24"/>
       <c r="E39" s="8">
         <v>4</v>
       </c>
@@ -1557,90 +1731,103 @@
       <c r="G39" s="8"/>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A40" s="22" t="s">
-        <v>30</v>
-      </c>
-      <c r="B40" s="22"/>
-      <c r="C40" s="22"/>
-      <c r="D40" s="22"/>
+      <c r="A40" s="24" t="s">
+        <v>33</v>
+      </c>
+      <c r="B40" s="24"/>
+      <c r="C40" s="24"/>
+      <c r="D40" s="24"/>
       <c r="E40" s="8">
+        <v>4</v>
+      </c>
+      <c r="F40" s="8"/>
+      <c r="G40" s="8"/>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A41" s="24" t="s">
+        <v>34</v>
+      </c>
+      <c r="B41" s="24"/>
+      <c r="C41" s="24"/>
+      <c r="D41" s="24"/>
+      <c r="E41" s="8">
         <f>E35+F35</f>
         <v>50</v>
       </c>
-      <c r="F40" s="8"/>
-      <c r="G40" s="8"/>
-    </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A41" s="22" t="s">
-        <v>31</v>
-      </c>
-      <c r="B41" s="22"/>
-      <c r="C41" s="22"/>
-      <c r="D41" s="22"/>
-      <c r="E41" s="8">
-        <v>60</v>
-      </c>
       <c r="F41" s="8"/>
       <c r="G41" s="8"/>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A42" s="22" t="s">
-        <v>32</v>
-      </c>
-      <c r="B42" s="22"/>
-      <c r="C42" s="22"/>
-      <c r="D42" s="22"/>
-      <c r="E42" s="9" t="str">
-        <f>IF(E40&gt;=E41,"MẤT CHUYÊN CẦN","ĐẠT CHUYÊN CẦN")</f>
+      <c r="A42" s="24" t="s">
+        <v>35</v>
+      </c>
+      <c r="B42" s="24"/>
+      <c r="C42" s="24"/>
+      <c r="D42" s="24"/>
+      <c r="E42" s="8">
+        <v>60</v>
+      </c>
+      <c r="F42" s="8"/>
+      <c r="G42" s="8"/>
+    </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A43" s="24" t="s">
+        <v>36</v>
+      </c>
+      <c r="B43" s="24"/>
+      <c r="C43" s="24"/>
+      <c r="D43" s="24"/>
+      <c r="E43" s="9" t="str">
+        <f>IF(E41&gt;=E42,"MẤT CHUYÊN CẦN","ĐẠT CHUYÊN CẦN")</f>
         <v>ĐẠT CHUYÊN CẦN</v>
       </c>
-      <c r="F42" s="9"/>
-      <c r="G42" s="9"/>
-    </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A43" s="22" t="s">
-        <v>33</v>
-      </c>
-      <c r="B43" s="22"/>
-      <c r="C43" s="22"/>
-      <c r="D43" s="22"/>
-      <c r="E43" s="8">
+      <c r="F43" s="9"/>
+      <c r="G43" s="9"/>
+    </row>
+    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A44" s="24" t="s">
+        <v>37</v>
+      </c>
+      <c r="B44" s="24"/>
+      <c r="C44" s="24"/>
+      <c r="D44" s="24"/>
+      <c r="E44" s="8">
         <v>0</v>
-      </c>
-      <c r="F43" s="8"/>
-      <c r="G43" s="8"/>
-    </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A44" s="22" t="s">
-        <v>34</v>
-      </c>
-      <c r="B44" s="22"/>
-      <c r="C44" s="22"/>
-      <c r="D44" s="22"/>
-      <c r="E44" s="8">
-        <v>19</v>
       </c>
       <c r="F44" s="8"/>
       <c r="G44" s="8"/>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A45" s="22" t="s">
-        <v>35</v>
-      </c>
-      <c r="B45" s="22"/>
-      <c r="C45" s="22"/>
-      <c r="D45" s="22"/>
-      <c r="E45" s="8" t="s">
-        <v>36</v>
+      <c r="A45" s="24" t="s">
+        <v>38</v>
+      </c>
+      <c r="B45" s="24"/>
+      <c r="C45" s="24"/>
+      <c r="D45" s="24"/>
+      <c r="E45" s="8">
+        <v>19</v>
       </c>
       <c r="F45" s="8"/>
       <c r="G45" s="8"/>
     </row>
+    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A46" s="24" t="s">
+        <v>39</v>
+      </c>
+      <c r="B46" s="24"/>
+      <c r="C46" s="24"/>
+      <c r="D46" s="24"/>
+      <c r="E46" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="F46" s="8"/>
+      <c r="G46" s="8"/>
+    </row>
   </sheetData>
-  <mergeCells count="22">
-    <mergeCell ref="A1:I1"/>
-    <mergeCell ref="A2:I2"/>
-    <mergeCell ref="A3:I3"/>
+  <mergeCells count="24">
+    <mergeCell ref="A1:K1"/>
+    <mergeCell ref="A2:K2"/>
+    <mergeCell ref="A3:K3"/>
     <mergeCell ref="A35:D35"/>
     <mergeCell ref="A37:D37"/>
     <mergeCell ref="E37:G37"/>
@@ -1660,182 +1847,11 @@
     <mergeCell ref="E44:G44"/>
     <mergeCell ref="A45:D45"/>
     <mergeCell ref="E45:G45"/>
+    <mergeCell ref="A46:D46"/>
+    <mergeCell ref="E46:G46"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="0"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G8"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
-  <cols>
-    <col min="1" max="1" width="13" customWidth="1"/>
-    <col min="2" max="3" width="8" customWidth="1"/>
-    <col min="4" max="4" width="10" customWidth="1"/>
-    <col min="5" max="5" width="24" customWidth="1"/>
-    <col min="6" max="6" width="30" customWidth="1"/>
-    <col min="7" max="7" width="26" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="32" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-      <c r="G1" s="1"/>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="2"/>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
-      <c r="G2" s="2"/>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B3" s="3"/>
-      <c r="C3" s="3"/>
-      <c r="D3" s="3"/>
-      <c r="E3" s="3"/>
-      <c r="F3" s="3"/>
-      <c r="G3" s="3"/>
-    </row>
-    <row r="4" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="E4" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="F4" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="G4" s="4" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="5" ht="103.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" s="5">
-        <v>46266</v>
-      </c>
-      <c r="B5" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="C5" s="24" t="s">
-        <v>43</v>
-      </c>
-      <c r="D5" s="7">
-        <v>0.3506944444444444</v>
-      </c>
-      <c r="E5" s="10" t="s">
-        <v>44</v>
-      </c>
-      <c r="F5" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="G5" s="25" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" s="5">
-        <v>46266</v>
-      </c>
-      <c r="B6" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="C6" s="26" t="s">
-        <v>45</v>
-      </c>
-      <c r="D6" s="7">
-        <v>0.7118055555555556</v>
-      </c>
-      <c r="E6" s="10" t="s">
-        <v>44</v>
-      </c>
-      <c r="F6" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="G6" s="25" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="7" ht="103.5" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" s="5">
-        <v>46267</v>
-      </c>
-      <c r="B7" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="C7" s="24" t="s">
-        <v>43</v>
-      </c>
-      <c r="D7" s="7">
-        <v>0.3680555555555556</v>
-      </c>
-      <c r="E7" s="10" t="s">
-        <v>47</v>
-      </c>
-      <c r="F7" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="G7" s="25" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" s="5">
-        <v>46267</v>
-      </c>
-      <c r="B8" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="C8" s="26" t="s">
-        <v>45</v>
-      </c>
-      <c r="D8" s="7">
-        <v>0.6875</v>
-      </c>
-      <c r="E8" s="10" t="s">
-        <v>44</v>
-      </c>
-      <c r="F8" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="G8" s="25" t="s">
-        <v>46</v>
-      </c>
-    </row>
-  </sheetData>
-  <autoFilter ref="A4:G8"/>
-  <mergeCells count="3">
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A3:G3"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup paperSize="9" orientation="landscape" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="0"/>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>